--- a/output/yearly_total_coral_cover_iteration_55_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_55_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.251400846453363</v>
+        <v>1.271133975308724</v>
       </c>
       <c r="C3" t="n">
-        <v>4.635485628528086</v>
+        <v>4.616478992973868</v>
       </c>
       <c r="D3" t="n">
-        <v>6.145480559378047</v>
+        <v>6.066459686663222</v>
       </c>
       <c r="E3" t="n">
-        <v>12.0323670343595</v>
+        <v>11.95407265494581</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.372769946245014</v>
+        <v>1.418797894104414</v>
       </c>
       <c r="C4" t="n">
-        <v>5.130553250485823</v>
+        <v>5.124153858618386</v>
       </c>
       <c r="D4" t="n">
-        <v>6.4579799402135</v>
+        <v>6.367415294845125</v>
       </c>
       <c r="E4" t="n">
-        <v>12.96130313694434</v>
+        <v>12.91036704756793</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.537997386259157</v>
+        <v>1.616856786347189</v>
       </c>
       <c r="C5" t="n">
-        <v>5.750711445793176</v>
+        <v>5.781727216371913</v>
       </c>
       <c r="D5" t="n">
-        <v>6.769892161866417</v>
+        <v>6.707556458317695</v>
       </c>
       <c r="E5" t="n">
-        <v>14.05860099391875</v>
+        <v>14.1061404610368</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.726149388820882</v>
+        <v>1.833246265556797</v>
       </c>
       <c r="C6" t="n">
-        <v>6.52612772070958</v>
+        <v>6.606414748981082</v>
       </c>
       <c r="D6" t="n">
-        <v>7.092511442825282</v>
+        <v>7.017186355136855</v>
       </c>
       <c r="E6" t="n">
-        <v>15.34478855235574</v>
+        <v>15.45684736967473</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.945182168100037</v>
+        <v>2.083536179679446</v>
       </c>
       <c r="C7" t="n">
-        <v>7.448872852325841</v>
+        <v>7.597828978060871</v>
       </c>
       <c r="D7" t="n">
-        <v>7.511334107494148</v>
+        <v>7.511342694177825</v>
       </c>
       <c r="E7" t="n">
-        <v>16.90538912792002</v>
+        <v>17.19270785191814</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.182566237697111</v>
+        <v>1.298144139570754</v>
       </c>
       <c r="C8" t="n">
-        <v>5.170188474707084</v>
+        <v>5.279644914172693</v>
       </c>
       <c r="D8" t="n">
-        <v>5.856076016604016</v>
+        <v>5.810970038109573</v>
       </c>
       <c r="E8" t="n">
-        <v>12.20883072900821</v>
+        <v>12.38875909185302</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.469662622617164</v>
+        <v>1.639151170105533</v>
       </c>
       <c r="C9" t="n">
-        <v>6.434663155045607</v>
+        <v>6.489072618760678</v>
       </c>
       <c r="D9" t="n">
-        <v>6.434666073072418</v>
+        <v>6.458679339788695</v>
       </c>
       <c r="E9" t="n">
-        <v>14.33899185073519</v>
+        <v>14.5869031286549</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.761577614857009</v>
+        <v>1.984048827224884</v>
       </c>
       <c r="C10" t="n">
-        <v>7.852641571140359</v>
+        <v>7.82071003696154</v>
       </c>
       <c r="D10" t="n">
-        <v>7.048291674508365</v>
+        <v>7.043191644024007</v>
       </c>
       <c r="E10" t="n">
-        <v>16.66251086050573</v>
+        <v>16.84795050821043</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.05189578267282</v>
+        <v>2.332823844772287</v>
       </c>
       <c r="C11" t="n">
-        <v>9.432727236815461</v>
+        <v>9.28540795675621</v>
       </c>
       <c r="D11" t="n">
-        <v>7.597994730980943</v>
+        <v>7.610463883354121</v>
       </c>
       <c r="E11" t="n">
-        <v>19.08261775046923</v>
+        <v>19.22869568488262</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.341878087665002</v>
+        <v>2.666766225860306</v>
       </c>
       <c r="C12" t="n">
-        <v>11.05942047125814</v>
+        <v>10.80210427938593</v>
       </c>
       <c r="D12" t="n">
-        <v>8.161632757483845</v>
+        <v>8.120327571114069</v>
       </c>
       <c r="E12" t="n">
-        <v>21.56293131640699</v>
+        <v>21.5891980763603</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.617296696084574</v>
+        <v>2.990837133700365</v>
       </c>
       <c r="C13" t="n">
-        <v>12.7788483659911</v>
+        <v>12.39901973425927</v>
       </c>
       <c r="D13" t="n">
-        <v>8.659356550611049</v>
+        <v>8.647282483990248</v>
       </c>
       <c r="E13" t="n">
-        <v>24.05550161268672</v>
+        <v>24.03713935194988</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.514139666782813</v>
+        <v>1.719805993345477</v>
       </c>
       <c r="C14" t="n">
-        <v>8.915437434329093</v>
+        <v>8.730417261986739</v>
       </c>
       <c r="D14" t="n">
-        <v>6.568108125906096</v>
+        <v>6.573183761537051</v>
       </c>
       <c r="E14" t="n">
-        <v>16.997685227018</v>
+        <v>17.02340701686927</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.52972000284921</v>
+        <v>1.750966665478272</v>
       </c>
       <c r="C15" t="n">
-        <v>9.756196350769018</v>
+        <v>9.448546072689195</v>
       </c>
       <c r="D15" t="n">
-        <v>6.61537927786558</v>
+        <v>6.621063597073169</v>
       </c>
       <c r="E15" t="n">
-        <v>17.90129563148381</v>
+        <v>17.82057633524064</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.758133423719273</v>
+        <v>2.030057902841555</v>
       </c>
       <c r="C16" t="n">
-        <v>11.58782340762821</v>
+        <v>11.17653002441105</v>
       </c>
       <c r="D16" t="n">
-        <v>7.183693388899974</v>
+        <v>7.241724495698002</v>
       </c>
       <c r="E16" t="n">
-        <v>20.52965022024745</v>
+        <v>20.4483124229506</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.398754859102686</v>
+        <v>1.624635370895792</v>
       </c>
       <c r="C17" t="n">
-        <v>10.73353600782376</v>
+        <v>10.30483623781031</v>
       </c>
       <c r="D17" t="n">
-        <v>6.70471831895204</v>
+        <v>6.777956697688853</v>
       </c>
       <c r="E17" t="n">
-        <v>18.83700918587849</v>
+        <v>18.70742830639495</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.575930867288107</v>
+        <v>1.848660379527872</v>
       </c>
       <c r="C18" t="n">
-        <v>12.53479760819059</v>
+        <v>12.00682351032371</v>
       </c>
       <c r="D18" t="n">
-        <v>7.215020958142489</v>
+        <v>7.228254917195736</v>
       </c>
       <c r="E18" t="n">
-        <v>21.32574943362119</v>
+        <v>21.08373880704731</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.563109242270644</v>
+        <v>1.846952138522482</v>
       </c>
       <c r="C19" t="n">
-        <v>13.40492059846454</v>
+        <v>12.81428154463558</v>
       </c>
       <c r="D19" t="n">
-        <v>7.328893874358077</v>
+        <v>7.341263895431587</v>
       </c>
       <c r="E19" t="n">
-        <v>22.29692371509326</v>
+        <v>22.00249757858965</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.721573139213122</v>
+        <v>2.055328088748868</v>
       </c>
       <c r="C20" t="n">
-        <v>15.34608124668655</v>
+        <v>14.71804742280282</v>
       </c>
       <c r="D20" t="n">
-        <v>7.787124615315276</v>
+        <v>7.822359540420694</v>
       </c>
       <c r="E20" t="n">
-        <v>24.85477900121495</v>
+        <v>24.59573505197238</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.014636252339079</v>
+        <v>1.224573181415217</v>
       </c>
       <c r="C21" t="n">
-        <v>11.21721364927504</v>
+        <v>10.81549230617428</v>
       </c>
       <c r="D21" t="n">
-        <v>6.512315403873749</v>
+        <v>6.556552955427111</v>
       </c>
       <c r="E21" t="n">
-        <v>18.74416530548786</v>
+        <v>18.59661844301661</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_55_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_55_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.271133975308724</v>
+        <v>1.281020174690489</v>
       </c>
       <c r="C3" t="n">
-        <v>4.616478992973868</v>
+        <v>4.595361599855519</v>
       </c>
       <c r="D3" t="n">
-        <v>6.066459686663222</v>
+        <v>6.043486790383846</v>
       </c>
       <c r="E3" t="n">
-        <v>11.95407265494581</v>
+        <v>11.91986856492985</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.418797894104414</v>
+        <v>1.444005240254988</v>
       </c>
       <c r="C4" t="n">
-        <v>5.124153858618386</v>
+        <v>5.045909911208651</v>
       </c>
       <c r="D4" t="n">
-        <v>6.367415294845125</v>
+        <v>6.294226695562061</v>
       </c>
       <c r="E4" t="n">
-        <v>12.91036704756793</v>
+        <v>12.7841418470257</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.616856786347189</v>
+        <v>1.658042432729722</v>
       </c>
       <c r="C5" t="n">
-        <v>5.781727216371913</v>
+        <v>5.621049407127788</v>
       </c>
       <c r="D5" t="n">
-        <v>6.707556458317695</v>
+        <v>6.632901025961409</v>
       </c>
       <c r="E5" t="n">
-        <v>14.1061404610368</v>
+        <v>13.91199286581892</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.833246265556797</v>
+        <v>1.895678277570824</v>
       </c>
       <c r="C6" t="n">
-        <v>6.606414748981082</v>
+        <v>6.317774664291252</v>
       </c>
       <c r="D6" t="n">
-        <v>7.017186355136855</v>
+        <v>6.986470692739803</v>
       </c>
       <c r="E6" t="n">
-        <v>15.45684736967473</v>
+        <v>15.19992363460188</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.083536179679446</v>
+        <v>2.157374368512256</v>
       </c>
       <c r="C7" t="n">
-        <v>7.597828978060871</v>
+        <v>7.131238035120611</v>
       </c>
       <c r="D7" t="n">
-        <v>7.511342694177825</v>
+        <v>7.435637333894761</v>
       </c>
       <c r="E7" t="n">
-        <v>17.19270785191814</v>
+        <v>16.72424973752763</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.298144139570754</v>
+        <v>1.367874330915396</v>
       </c>
       <c r="C8" t="n">
-        <v>5.279644914172693</v>
+        <v>4.766948556243815</v>
       </c>
       <c r="D8" t="n">
-        <v>5.810970038109573</v>
+        <v>5.794404064238202</v>
       </c>
       <c r="E8" t="n">
-        <v>12.38875909185302</v>
+        <v>11.92922695139741</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.639151170105533</v>
+        <v>1.743237122810568</v>
       </c>
       <c r="C9" t="n">
-        <v>6.489072618760678</v>
+        <v>5.813905051855068</v>
       </c>
       <c r="D9" t="n">
-        <v>6.458679339788695</v>
+        <v>6.395822113135843</v>
       </c>
       <c r="E9" t="n">
-        <v>14.5869031286549</v>
+        <v>13.95296428780148</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.984048827224884</v>
+        <v>2.143523044254251</v>
       </c>
       <c r="C10" t="n">
-        <v>7.82071003696154</v>
+        <v>7.040093471719473</v>
       </c>
       <c r="D10" t="n">
-        <v>7.043191644024007</v>
+        <v>7.088291706234162</v>
       </c>
       <c r="E10" t="n">
-        <v>16.84795050821043</v>
+        <v>16.27190822220788</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.332823844772287</v>
+        <v>2.538686633771546</v>
       </c>
       <c r="C11" t="n">
-        <v>9.28540795675621</v>
+        <v>8.420529478123067</v>
       </c>
       <c r="D11" t="n">
-        <v>7.610463883354121</v>
+        <v>7.726477732499936</v>
       </c>
       <c r="E11" t="n">
-        <v>19.22869568488262</v>
+        <v>18.68569384439455</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.666766225860306</v>
+        <v>2.937067436681352</v>
       </c>
       <c r="C12" t="n">
-        <v>10.80210427938593</v>
+        <v>9.944741215063349</v>
       </c>
       <c r="D12" t="n">
-        <v>8.120327571114069</v>
+        <v>8.353836421749845</v>
       </c>
       <c r="E12" t="n">
-        <v>21.5891980763603</v>
+        <v>21.23564507349455</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.990837133700365</v>
+        <v>3.324814888323588</v>
       </c>
       <c r="C13" t="n">
-        <v>12.39901973425927</v>
+        <v>11.50254265837405</v>
       </c>
       <c r="D13" t="n">
-        <v>8.647282483990248</v>
+        <v>8.926020060214544</v>
       </c>
       <c r="E13" t="n">
-        <v>24.03713935194988</v>
+        <v>23.75337760691218</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.719805993345477</v>
+        <v>1.913740434842393</v>
       </c>
       <c r="C14" t="n">
-        <v>8.730417261986739</v>
+        <v>8.119819277330434</v>
       </c>
       <c r="D14" t="n">
-        <v>6.573183761537051</v>
+        <v>6.815125665771637</v>
       </c>
       <c r="E14" t="n">
-        <v>17.02340701686927</v>
+        <v>16.84868537794446</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.750966665478272</v>
+        <v>1.974009926406104</v>
       </c>
       <c r="C15" t="n">
-        <v>9.448546072689195</v>
+        <v>8.860243578396336</v>
       </c>
       <c r="D15" t="n">
-        <v>6.621063597073169</v>
+        <v>6.921331132417055</v>
       </c>
       <c r="E15" t="n">
-        <v>17.82057633524064</v>
+        <v>17.7555846372195</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.030057902841555</v>
+        <v>2.293136835148573</v>
       </c>
       <c r="C16" t="n">
-        <v>11.17653002441105</v>
+        <v>10.54003353531671</v>
       </c>
       <c r="D16" t="n">
-        <v>7.241724495698002</v>
+        <v>7.475822235775655</v>
       </c>
       <c r="E16" t="n">
-        <v>20.4483124229506</v>
+        <v>20.30899260624094</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.624635370895792</v>
+        <v>1.839314141383442</v>
       </c>
       <c r="C17" t="n">
-        <v>10.30483623781031</v>
+        <v>9.824633983232065</v>
       </c>
       <c r="D17" t="n">
-        <v>6.777956697688853</v>
+        <v>7.003709582280406</v>
       </c>
       <c r="E17" t="n">
-        <v>18.70742830639495</v>
+        <v>18.66765770689591</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.848660379527872</v>
+        <v>2.093891138571682</v>
       </c>
       <c r="C18" t="n">
-        <v>12.00682351032371</v>
+        <v>11.48358143639128</v>
       </c>
       <c r="D18" t="n">
-        <v>7.228254917195736</v>
+        <v>7.510841176386137</v>
       </c>
       <c r="E18" t="n">
-        <v>21.08373880704731</v>
+        <v>21.0883137513491</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.846952138522482</v>
+        <v>2.092879938436308</v>
       </c>
       <c r="C19" t="n">
-        <v>12.81428154463558</v>
+        <v>12.30252591884284</v>
       </c>
       <c r="D19" t="n">
-        <v>7.341263895431587</v>
+        <v>7.634266497764047</v>
       </c>
       <c r="E19" t="n">
-        <v>22.00249757858965</v>
+        <v>22.0296723550432</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.055328088748868</v>
+        <v>2.316374803308094</v>
       </c>
       <c r="C20" t="n">
-        <v>14.71804742280282</v>
+        <v>14.14754401438796</v>
       </c>
       <c r="D20" t="n">
-        <v>7.822359540420694</v>
+        <v>8.115322872844985</v>
       </c>
       <c r="E20" t="n">
-        <v>24.59573505197238</v>
+        <v>24.57924169054104</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.224573181415217</v>
+        <v>1.370706327192355</v>
       </c>
       <c r="C21" t="n">
-        <v>10.81549230617428</v>
+        <v>10.39778811044839</v>
       </c>
       <c r="D21" t="n">
-        <v>6.556552955427111</v>
+        <v>6.808498868767971</v>
       </c>
       <c r="E21" t="n">
-        <v>18.59661844301661</v>
+        <v>18.57699330640872</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_55_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_55_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.281020174690489</v>
+        <v>2.581190950935158</v>
       </c>
       <c r="C3" t="n">
-        <v>4.595361599855519</v>
+        <v>7.688181251037787</v>
       </c>
       <c r="D3" t="n">
-        <v>6.043486790383846</v>
+        <v>8.227612980314156</v>
       </c>
       <c r="E3" t="n">
-        <v>11.91986856492985</v>
+        <v>18.4969851822871</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.444005240254988</v>
+        <v>1.047024343643385</v>
       </c>
       <c r="C4" t="n">
-        <v>5.045909911208651</v>
+        <v>4.426956856830156</v>
       </c>
       <c r="D4" t="n">
-        <v>6.294226695562061</v>
+        <v>5.77500325866639</v>
       </c>
       <c r="E4" t="n">
-        <v>12.7841418470257</v>
+        <v>11.24898445913993</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.658042432729722</v>
+        <v>1.117897310504625</v>
       </c>
       <c r="C5" t="n">
-        <v>5.621049407127788</v>
+        <v>4.962080813343825</v>
       </c>
       <c r="D5" t="n">
-        <v>6.632901025961409</v>
+        <v>6.137537358460179</v>
       </c>
       <c r="E5" t="n">
-        <v>13.91199286581892</v>
+        <v>12.21751548230863</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.895678277570824</v>
+        <v>1.192585501776249</v>
       </c>
       <c r="C6" t="n">
-        <v>6.317774664291252</v>
+        <v>5.603820663293636</v>
       </c>
       <c r="D6" t="n">
-        <v>6.986470692739803</v>
+        <v>6.551812360356005</v>
       </c>
       <c r="E6" t="n">
-        <v>15.19992363460188</v>
+        <v>13.34821852542589</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.157374368512256</v>
+        <v>1.265476353361709</v>
       </c>
       <c r="C7" t="n">
-        <v>7.131238035120611</v>
+        <v>6.355736744575827</v>
       </c>
       <c r="D7" t="n">
-        <v>7.435637333894761</v>
+        <v>7.012046920435851</v>
       </c>
       <c r="E7" t="n">
-        <v>16.72424973752763</v>
+        <v>14.63326001837339</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.367874330915396</v>
+        <v>1.342174332064861</v>
       </c>
       <c r="C8" t="n">
-        <v>4.766948556243815</v>
+        <v>7.22465602344925</v>
       </c>
       <c r="D8" t="n">
-        <v>5.794404064238202</v>
+        <v>7.423663832907762</v>
       </c>
       <c r="E8" t="n">
-        <v>11.92922695139741</v>
+        <v>15.99049418842187</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.743237122810568</v>
+        <v>1.424210136554056</v>
       </c>
       <c r="C9" t="n">
-        <v>5.813905051855068</v>
+        <v>8.252589772886111</v>
       </c>
       <c r="D9" t="n">
-        <v>6.395822113135843</v>
+        <v>8.014097260476465</v>
       </c>
       <c r="E9" t="n">
-        <v>13.95296428780148</v>
+        <v>17.69089716991663</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.143523044254251</v>
+        <v>0.9220181739204343</v>
       </c>
       <c r="C10" t="n">
-        <v>7.040093471719473</v>
+        <v>6.252790398256105</v>
       </c>
       <c r="D10" t="n">
-        <v>7.088291706234162</v>
+        <v>6.34688109823112</v>
       </c>
       <c r="E10" t="n">
-        <v>16.27190822220788</v>
+        <v>13.52168967040766</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.538686633771546</v>
+        <v>0.8344168262704914</v>
       </c>
       <c r="C11" t="n">
-        <v>8.420529478123067</v>
+        <v>6.528681138103544</v>
       </c>
       <c r="D11" t="n">
-        <v>7.726477732499936</v>
+        <v>6.304096533280043</v>
       </c>
       <c r="E11" t="n">
-        <v>18.68569384439455</v>
+        <v>13.66719449765408</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.937067436681352</v>
+        <v>0.8785365680993433</v>
       </c>
       <c r="C12" t="n">
-        <v>9.944741215063349</v>
+        <v>7.665927861226007</v>
       </c>
       <c r="D12" t="n">
-        <v>8.353836421749845</v>
+        <v>6.855465678939137</v>
       </c>
       <c r="E12" t="n">
-        <v>21.23564507349455</v>
+        <v>15.39993010826449</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.324814888323588</v>
+        <v>0.6855347869214629</v>
       </c>
       <c r="C13" t="n">
-        <v>11.50254265837405</v>
+        <v>7.284803584960352</v>
       </c>
       <c r="D13" t="n">
-        <v>8.926020060214544</v>
+        <v>6.36915695364048</v>
       </c>
       <c r="E13" t="n">
-        <v>23.75337760691218</v>
+        <v>14.33949532552229</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.913740434842393</v>
+        <v>0.7313136823704915</v>
       </c>
       <c r="C14" t="n">
-        <v>8.119819277330434</v>
+        <v>8.52907062532276</v>
       </c>
       <c r="D14" t="n">
-        <v>6.815125665771637</v>
+        <v>6.920516281822532</v>
       </c>
       <c r="E14" t="n">
-        <v>16.84868537794446</v>
+        <v>16.18090058951578</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.974009926406104</v>
+        <v>0.7002119150999526</v>
       </c>
       <c r="C15" t="n">
-        <v>8.860243578396336</v>
+        <v>9.216352923157782</v>
       </c>
       <c r="D15" t="n">
-        <v>6.921331132417055</v>
+        <v>7.088807473284518</v>
       </c>
       <c r="E15" t="n">
-        <v>17.7555846372195</v>
+        <v>17.00537231154225</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.293136835148573</v>
+        <v>0.7619736631741195</v>
       </c>
       <c r="C16" t="n">
-        <v>10.54003353531671</v>
+        <v>10.83939786277269</v>
       </c>
       <c r="D16" t="n">
-        <v>7.475822235775655</v>
+        <v>7.721239526883273</v>
       </c>
       <c r="E16" t="n">
-        <v>20.30899260624094</v>
+        <v>19.32261105283008</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.839314141383442</v>
+        <v>0.4637972504402782</v>
       </c>
       <c r="C17" t="n">
-        <v>9.824633983232065</v>
+        <v>8.253179885475321</v>
       </c>
       <c r="D17" t="n">
-        <v>7.003709582280406</v>
+        <v>6.527080889345622</v>
       </c>
       <c r="E17" t="n">
-        <v>18.66765770689591</v>
+        <v>15.24405802526122</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.093891138571682</v>
+        <v>0.3523492510541803</v>
       </c>
       <c r="C18" t="n">
-        <v>11.48358143639128</v>
+        <v>7.383429959328987</v>
       </c>
       <c r="D18" t="n">
-        <v>7.510841176386137</v>
+        <v>6.115227909937042</v>
       </c>
       <c r="E18" t="n">
-        <v>21.0883137513491</v>
+        <v>13.85100712032021</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.092879938436308</v>
+        <v>0.408446314874843</v>
       </c>
       <c r="C19" t="n">
-        <v>12.30252591884284</v>
+        <v>9.199614124800373</v>
       </c>
       <c r="D19" t="n">
-        <v>7.634266497764047</v>
+        <v>6.792977437563828</v>
       </c>
       <c r="E19" t="n">
-        <v>22.0296723550432</v>
+        <v>16.40103787723904</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.316374803308094</v>
+        <v>0.4606458403096459</v>
       </c>
       <c r="C20" t="n">
-        <v>14.14754401438796</v>
+        <v>11.11520024532675</v>
       </c>
       <c r="D20" t="n">
-        <v>8.115322872844985</v>
+        <v>7.484422345664857</v>
       </c>
       <c r="E20" t="n">
-        <v>24.57924169054104</v>
+        <v>19.06026843130125</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.370706327192355</v>
+        <v>0.5070039669041803</v>
       </c>
       <c r="C21" t="n">
-        <v>10.39778811044839</v>
+        <v>13.02981443562592</v>
       </c>
       <c r="D21" t="n">
-        <v>6.808498868767971</v>
+        <v>8.208755801858153</v>
       </c>
       <c r="E21" t="n">
-        <v>18.57699330640872</v>
+        <v>21.74557420438826</v>
       </c>
     </row>
   </sheetData>
